--- a/data_extactor/batch_10_fa/batch_0035_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0035_fa.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Secondary School Teachers, Except Special and Career/Technical Education (معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای)</t>
+          <t>معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای (Secondary School Teachers, Except Special and Career/Technical Education)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ABC programming language | Blackboard software | Common Curriculum | Desmos | Email software (نرم‌افزار ایمیل) | Flipgrid | Geogebra | Google Classroom | Google Drive | Google Meet | Instructional software (نرم‌افزار آموزشی) | Logo design software (نرم‌افزار طراحی لوگو) | Microsoft Excel | Microsoft Office software (نرم‌افزار Microsoft Office) | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | Moodle | Nearpod | PowerSchool SIS | Schoology | Screencastify | Video editing software (نرم‌افزار ویرایش ویدیو) | Web browser software (نرم‌افزار مرورگر وب)</t>
+          <t>ABC programming language | نرم‌افزار Blackboard | Common Curriculum | Desmos | نرم‌افزار ایمیل | Flipgrid | Geogebra | Google Classroom | Google Drive | Google Meet | نرم‌افزار آموزشی | نرم‌افزار طراحی لوگو | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | Moodle | Nearpod | PowerSchool SIS | Schoology | Screencastify | نرم‌افزار ویرایش ویدیو | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Learning Strategies (راهبردهای یادگیری) | Speaking (سخن‌وری) | Active Listening (گوش دادن فعال) | Reading Comprehension (درک مطلب) | Critical Thinking (تفکر انتقادی) | Monitoring (پایش) | Active Learning (یادگیری فعال) | Writing (نوشتن)</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Education and Training (آموزش و پرورش) | English Language (زبان انگلیسی) | Customer and Personal Service (خدمات مشتری و شخصی) | Computers and Electronics (کامپیوتر و الکترونیک) | Psychology (روان‌شناسی) | Sociology and Anthropology (جامعه‌شناسی و انسان‌شناسی) | History and Archeology (تاریخ و باستان‌شناسی)</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Oral Expression (بیان شفاهی) | Oral Comprehension (درک شفاهی) | Written Comprehension (درک کتبی) | Written Expression (بیان کتبی) | Speech Recognition (تشخیص گفتار) | Speech Clarity (وضوح گفتار) | Deductive Reasoning (استدلال قیاسی) | Near Vision (دید نزدیک) | Problem Sensitivity (حساسیت به مسئله) | Inductive Reasoning (استدلال استقرایی) | Information Ordering (ترتیب‌دهی اطلاعات) | Fluency of Ideas (روانی ایده‌ها) | Originality (خلاقیت) | Category Flexibility (انعطاف‌پذیری دسته‌بندی) | Far Vision (دید دور) | Selective Attention (توجه انتخابی) | Mathematical Reasoning (استدلال ریاضی)</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بینایی نزدیک | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-Mail (ایمیل) | Contact With Others (ارتباط با دیگران) | Face-to-Face Discussions with Individuals and Within Teams (بحث‌های رودررو با افراد و درون تیم‌ها) | Indoors, Environmentally Controlled (محیط داخلی، دارای کنترل محیطی) | Public Speaking (سخنرانی عمومی) | Freedom to Make Decisions (آزادی در تصمیم‌گیری) | Work With or Contribute to a Work Group or Team (کار با یا مشارکت در یک گروه کاری یا تیم) | Physical Proximity (مجاورت فیزیکی) | Coordinate or Lead Others in Accomplishing Work Activities (هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری) | Determine Tasks, Priorities and Goals (تعیین وظایف، اولویت‌ها و اهداف) | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable (قرار گرفتن در معرض صداها و سطوح نویز حواس‌پرت‌کن یا ناراحت‌کننده) | Frequency of Decision Making (تکرار تصمیم‌گیری) | Telephone Conversations (مکالمات تلفنی)</t>
+          <t>ایمیل | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | سخنرانی عمومی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors (مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم) | Art, Drama, and Music Teachers, Postsecondary (معلمان هنر، نمایش و موسیقی، پس از متوسطه) | Career/Technical Education Teachers, Middle School (معلمان آموزش فنی/حرفه‌ای، دوره راهنمایی) | Career/Technical Education Teachers, Secondary School (معلمان آموزش فنی/حرفه‌ای، دوره متوسطه) | Education Teachers, Postsecondary (معلمان علوم تربیتی، پس از متوسطه) | Elementary School Teachers, Except Special Education (معلمان دبستان، به استثنای آموزش ویژه) | English Language and Literature Teachers, Postsecondary (معلمان زبان و ادبیات انگلیسی، پس از متوسطه) | Instructional Coordinators (هماهنگ‌کنندگان آموزشی) | Kindergarten Teachers, Except Special Education (معلمان کودکستان، به استثنای آموزش ویژه) | Middle School Teachers, Except Special and Career/Technical Education (معلمان راهنمایی، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Self-Enrichment Teachers (معلمان دوره‌های فوق‌برنامه) | Special Education Teachers, Elementary School (معلمان آموزش ویژه، دبستان) | Special Education Teachers, Kindergarten (معلمان آموزش ویژه، کودکستان) | Special Education Teachers, Middle School (معلمان آموزش ویژه، راهنمایی) | Special Education Teachers, Preschool (معلمان آموزش ویژه، پیش‌دبستانی) | Special Education Teachers, Secondary School (معلمان آموزش ویژه، متوسطه) | Teaching Assistants, Postsecondary (دستیاران آموزشی، پس از متوسطه) | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education (دستیاران آموزشی، پیش‌دبستانی، دبستان، راهنمایی و متوسطه، به استثنای آموزش ویژه) | Teaching Assistants, Special Education (دستیاران آموزشی، آموزش ویژه) | Tutors (مدرسان خصوصی)</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | مدرسان هنر، نمایش و موسیقی، آموزش عالی | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Career/Technical Education Teachers, Secondary School (معلمان آموزش فنی/حرفه‌ای، دوره متوسطه)</t>
+          <t>معلمان آموزش فنی/حرفه‌ای، دوره متوسطه (Career/Technical Education Teachers, Secondary School)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD Civil 3D | Blackboard Learn | Collaborative editing software (نرم‌افزار ویرایش مشارکتی) | Course management system software (نرم‌افزار سیستم مدیریت دوره) | DOC Cop | Desire2Learn LMS software | Edmodo | Edpuzzle | Email software (نرم‌افزار ایمیل) | Google Docs | Image scanning software (نرم‌افزار اسکن تصویر) | Kahoot! | Learning management system LMS (نرم‌افزار سیستم مدیریت یادگیری LMS) | Microsoft Excel | Microsoft Office software (نرم‌افزار Microsoft Office) | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Padlet | Sakai CLE | Web browser software (نرم‌افزار مرورگر وب) | iParadigms Turnitin</t>
+          <t>Autodesk AutoCAD Civil 3D | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | Edmodo | Edpuzzle | نرم‌افزار ایمیل | Google Docs | نرم‌افزار اسکن تصویر | Kahoot! | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Padlet | Sakai CLE | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Reading Comprehension (درک مطلب) | Active Listening (گوش دادن فعال) | Speaking (سخن‌وری) | Learning Strategies (راهبردهای یادگیری) | Writing (نوشتن) | Monitoring (پایش) | Critical Thinking (تفکر انتقادی) | Active Learning (یادگیری فعال) | Mathematics (ریاضیات)</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | راهبردهای یادگیری | نگارش | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Education and Training (آموزش و پرورش) | English Language (زبان انگلیسی) | Computers and Electronics (کامپیوتر و الکترونیک) | Customer and Personal Service (خدمات مشتری و شخصی) | Public Safety and Security (ایمنی و امنیت عمومی) | Administration and Management (اداره و مدیریت) | Mathematics (ریاضیات) | Psychology (روان‌شناسی)</t>
+          <t>آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | مدیریت و اداره | ریاضیات | روان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oral Expression (بیان شفاهی) | Oral Comprehension (درک شفاهی) | Written Comprehension (درک کتبی) | Speech Clarity (وضوح گفتار) | Written Expression (بیان کتبی) | Problem Sensitivity (حساسیت به مسئله) | Inductive Reasoning (استدلال استقرایی) | Speech Recognition (تشخیص گفتار) | Deductive Reasoning (استدلال قیاسی) | Near Vision (دید نزدیک) | Information Ordering (ترتیب‌دهی اطلاعات) | Fluency of Ideas (روانی ایده‌ها) | Category Flexibility (انعطاف‌پذیری دسته‌بندی) | Far Vision (دید دور) | Originality (خلاقیت) | Selective Attention (توجه انتخابی) | Time Sharing (اشتراک زمانی) | Flexibility of Closure (انعطاف‌پذیری در بستار) | Speed of Closure (سرعت بستار) | Memorization (حافظه) | Mathematical Reasoning (استدلال ریاضی)</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بینایی دور | اصالت | توجه انتخابی | تقسیم توجه | انعطاف‌پذیری بستار | سرعت بستار | حفظ کردن | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-Mail (ایمیل) | Contact With Others (ارتباط با دیگران) | Public Speaking (سخنرانی عمومی) | Face-to-Face Discussions with Individuals and Within Teams (بحث‌های رودررو با افراد و درون تیم‌ها) | Frequency of Decision Making (تکرار تصمیم‌گیری) | Determine Tasks, Priorities and Goals (تعیین وظایف، اولویت‌ها و اهداف) | Freedom to Make Decisions (آزادی در تصمیم‌گیری) | Physical Proximity (مجاورت فیزیکی) | Coordinate or Lead Others in Accomplishing Work Activities (هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری) | Time Pressure (فشار زمانی) | Impact of Decisions on Co-workers or Company Results (تأثیر تصمیمات بر همکاران یا نتایج شرکت) | Work With or Contribute to a Work Group or Team (کار با یا مشارکت در یک گروه کاری یا تیم) | Dealing With Unpleasant, Angry, or Discourteous People (سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب) | Health and Safety of Other Workers (سلامت و ایمنی سایر کارکنان) | Indoors, Environmentally Controlled (محیط داخلی، دارای کنترل محیطی) | Importance of Being Exact or Accurate (اهمیت دقیق یا صحیح بودن) | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable (قرار گرفتن در معرض صداها و سطوح نویز حواس‌پرت‌کن یا ناراحت‌کننده) | Telephone Conversations (مکالمات تلفنی) | Conflict Situations (موقعیت‌های تعارض)</t>
+          <t>ایمیل | ارتباط با دیگران | سخنرانی عمومی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | مکالمات تلفنی | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Adapted Physical Education Specialists (متخصصان تربیت بدنی تطبیقی) | Business Teachers, Postsecondary (معلمان کسب‌وکار، پس از متوسطه) | Career/Technical Education Teachers, Middle School (معلمان آموزش فنی/حرفه‌ای، دوره راهنمایی) | Career/Technical Education Teachers, Postsecondary (معلمان آموزش فنی/حرفه‌ای، پس از متوسطه) | Computer Science Teachers, Postsecondary (معلمان علوم کامپیوتر، پس از متوسطه) | Educational, Guidance, and Career Counselors and Advisors (مشاوران و راهنمایان آموزشی، تحصیلی و شغلی) | Elementary School Teachers, Except Special Education (معلمان دبستان، به استثنای آموزش ویژه) | Family and Consumer Sciences Teachers, Postsecondary (معلمان علوم خانواده و مصرف‌کننده، پس از متوسطه) | Instructional Coordinators (هماهنگ‌کنندگان آموزشی) | Middle School Teachers, Except Special and Career/Technical Education (معلمان راهنمایی، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Secondary School Teachers, Except Special and Career/Technical Education (معلمان متوسطه، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Self-Enrichment Teachers (معلمان دوره‌های فوق‌برنامه) | Special Education Teachers, Elementary School (معلمان آموزش ویژه، دبستان) | Special Education Teachers, Kindergarten (معلمان آموزش ویژه، کودکستان) | Special Education Teachers, Middle School (معلمان آموزش ویژه، راهنمایی) | Special Education Teachers, Secondary School (معلمان آموزش ویژه، متوسطه) | Teaching Assistants, Postsecondary (دستیاران آموزشی، پس از متوسطه) | Teaching Assistants, Special Education (دستیاران آموزشی، آموزش ویژه) | Training and Development Specialists (متخصصان آموزش و توسعه) | Tutors (مدرسان خصوصی)</t>
+          <t>متخصصان تربیت بدنی تطبیقی | اساتید کسب‌وکار، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | اساتید علوم رایانه، پس از متوسطه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان آموزشی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، آموزش استثنایی | متخصصان آموزش و توسعه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Special Education Teachers, Preschool (معلمان آموزش ویژه، پیش‌دبستانی)</t>
+          <t>معلمان آموزش ویژه، پیش‌دبستانی (Special Education Teachers, Preschool)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>American Sign Language Browser (مرورگر زبان اشاره آمریکایی) | Children's educational software (نرم‌افزار آموزشی کودکان) | Drawing software (نرم‌افزار طراحی) | Email software (نرم‌افزار ایمیل) | Microsoft Excel | Microsoft Office software (نرم‌افزار Microsoft Office) | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Screen magnification software (نرم‌افزار بزرگ‌نمایی صفحه) | Screen reader software (نرم‌افزار صفحه‌خوان) | Web browser software (نرم‌افزار مرورگر وب)</t>
+          <t>American Sign Language Browser (مرورگر زبان اشاره آمریکایی) | Children's educational software | نرم‌افزار طراحی | نرم‌افزار ایمیل | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار بزرگ‌نمایی صفحه | نرم‌افزار صفحه‌خوان | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Speaking (سخن‌وری) | Active Listening (گوش دادن فعال) | Reading Comprehension (درک مطلب) | Critical Thinking (تفکر انتقادی) | Writing (نوشتن) | Learning Strategies (راهبردهای یادگیری) | Monitoring (پایش) | Active Learning (یادگیری فعال)</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | راهبردهای یادگیری | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>English Language (زبان انگلیسی) | Education and Training (آموزش و پرورش) | Psychology (روان‌شناسی) | Public Safety and Security (ایمنی و امنیت عمومی) | Therapy and Counseling (درمان و مشاوره) | Computers and Electronics (کامپیوتر و الکترونیک) | Administrative (اداری) | Customer and Personal Service (خدمات مشتری و شخصی)</t>
+          <t>زبان انگلیسی | آموزش و پرورش | روان‌شناسی | ایمنی و امنیت عمومی | درمان و مشاوره | رایانه و الکترونیک | اداری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oral Expression (بیان شفاهی) | Oral Comprehension (درک شفاهی) | Written Comprehension (درک کتبی) | Problem Sensitivity (حساسیت به مسئله) | Speech Clarity (وضوح گفتار) | Deductive Reasoning (استدلال قیاسی) | Inductive Reasoning (استدلال استقرایی) | Written Expression (بیان کتبی) | Speech Recognition (تشخیص گفتار) | Selective Attention (توجه انتخابی) | Information Ordering (ترتیب‌دهی اطلاعات) | Near Vision (دید نزدیک) | Fluency of Ideas (روانی ایده‌ها) | Time Sharing (اشتراک زمانی) | Category Flexibility (انعطاف‌پذیری دسته‌بندی)</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | توجه انتخابی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | تقسیم توجه | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Face-to-Face Discussions with Individuals and Within Teams (بحث‌های رودررو با افراد و درون تیم‌ها) | Contact With Others (ارتباط با دیگران) | Work With or Contribute to a Work Group or Team (کار با یا مشارکت در یک گروه کاری یا تیم) | E-Mail (ایمیل) | Physical Proximity (مجاورت فیزیکی) | Indoors, Environmentally Controlled (محیط داخلی، دارای کنترل محیطی) | Frequency of Decision Making (تکرار تصمیم‌گیری) | Freedom to Make Decisions (آزادی در تصمیم‌گیری) | Determine Tasks, Priorities and Goals (تعیین وظایف، اولویت‌ها و اهداف) | Impact of Decisions on Co-workers or Company Results (تأثیر تصمیمات بر همکاران یا نتایج شرکت) | Telephone Conversations (مکالمات تلفنی) | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable (قرار گرفتن در معرض صداها و سطوح نویز حواس‌پرت‌کن یا ناراحت‌کننده)</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Adapted Physical Education Specialists (متخصصان تربیت بدنی تطبیقی) | Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors (مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم) | Career/Technical Education Teachers, Middle School (معلمان آموزش فنی/حرفه‌ای، دوره راهنمایی) | Education Teachers, Postsecondary (معلمان علوم تربیتی، پس از متوسطه) | Educational, Guidance, and Career Counselors and Advisors (مشاوران و راهنمایان آموزشی، تحصیلی و شغلی) | Elementary School Teachers, Except Special Education (معلمان دبستان، به استثنای آموزش ویژه) | Instructional Coordinators (هماهنگ‌کنندگان آموزشی) | Kindergarten Teachers, Except Special Education (معلمان کودکستان، به استثنای آموزش ویژه) | Middle School Teachers, Except Special and Career/Technical Education (معلمان راهنمایی، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Preschool Teachers, Except Special Education (معلمان پیش‌دبستانی، به استثنای آموزش ویژه) | School Psychologists (روان‌شناسان مدرسه) | Secondary School Teachers, Except Special and Career/Technical Education (معلمان متوسطه، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Self-Enrichment Teachers (معلمان دوره‌های فوق‌برنامه) | Special Education Teachers, Elementary School (معلمان آموزش ویژه، دبستان) | Special Education Teachers, Kindergarten (معلمان آموزش ویژه، کودکستان) | Special Education Teachers, Middle School (معلمان آموزش ویژه، راهنمایی) | Special Education Teachers, Secondary School (معلمان آموزش ویژه، متوسطه) | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education (دستیاران آموزشی، پیش‌دبستانی، دبستان، راهنمایی و متوسطه، به استثنای آموزش ویژه) | Teaching Assistants, Special Education (دستیاران آموزشی، آموزش ویژه) | Tutors (مدرسان خصوصی)</t>
+          <t>متخصصان تربیت بدنی تطبیقی | مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | روان‌شناسان مدرسه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Special Education Teachers, Kindergarten (معلمان آموزش ویژه، کودکستان)</t>
+          <t>معلمان آموزش ویژه، کودکستان (Special Education Teachers, Kindergarten)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>American Sign Language Browser (مرورگر زبان اشاره آمریکایی) | Children's educational software (نرم‌افزار آموزشی کودکان) | Drawing software (نرم‌افزار طراحی) | EasyCBM | Email software (نرم‌افزار ایمیل) | Individualized Educational Program IEP software (نرم‌افزار برنامه آموزش فردی IEP) | Microsoft Excel | Microsoft Office software (نرم‌افزار Microsoft Office) | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Nuance Dragon NaturallySpeaking | Rethink Ed | Scientific Learning Fast ForWord | Screen magnification software (نرم‌افزار بزرگ‌نمایی صفحه) | Screen reader software (نرم‌افزار صفحه‌خوان) | Synapse outSPOKEN | The vOICe Learning Edition | Voice activated software (نرم‌افزار فعال‌شونده با صدا) | Web browser software (نرم‌افزار مرورگر وب) | goQ WordQ</t>
+          <t>American Sign Language Browser (مرورگر زبان اشاره آمریکایی) | Children's educational software | نرم‌افزار طراحی | EasyCBM | نرم‌افزار ایمیل | Individualized Educational Program IEP software (نرم‌افزار برنامه آموزش فردی IEP) | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Nuance Dragon NaturallySpeaking | Rethink Ed | Scientific Learning Fast ForWord | نرم‌افزار بزرگ‌نمایی صفحه | نرم‌افزار صفحه‌خوان | Synapse outSPOKEN | The vOICe Learning Edition | نرم‌افزار فعال‌شونده با صدا | نرم‌افزار مرورگر وب | goQ WordQ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Speaking (سخن‌وری) | Active Listening (گوش دادن فعال) | Reading Comprehension (درک مطلب) | Critical Thinking (تفکر انتقادی) | Learning Strategies (راهبردهای یادگیری) | Writing (نوشتن) | Active Learning (یادگیری فعال) | Monitoring (پایش)</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Education and Training (آموزش و پرورش) | Psychology (روان‌شناسی) | English Language (زبان انگلیسی) | Therapy and Counseling (درمان و مشاوره) | Customer and Personal Service (خدمات مشتری و شخصی) | Sociology and Anthropology (جامعه‌شناسی و انسان‌شناسی) | Mathematics (ریاضیات) | Computers and Electronics (کامپیوتر و الکترونیک)</t>
+          <t>آموزش و پرورش | روان‌شناسی | زبان انگلیسی | درمان و مشاوره | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oral Comprehension (درک شفاهی) | Written Comprehension (درک کتبی) | Oral Expression (بیان شفاهی) | Written Expression (بیان کتبی) | Deductive Reasoning (استدلال قیاسی) | Inductive Reasoning (استدلال استقرایی) | Information Ordering (ترتیب‌دهی اطلاعات) | Problem Sensitivity (حساسیت به مسئله) | Near Vision (دید نزدیک) | Speech Clarity (وضوح گفتار) | Speech Recognition (تشخیص گفتار) | Category Flexibility (انعطاف‌پذیری دسته‌بندی) | Fluency of Ideas (روانی ایده‌ها) | Originality (خلاقیت) | Selective Attention (توجه انتخابی) | Time Sharing (اشتراک زمانی) | Visualization (تجسم) | Memorization (حافظه)</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Face-to-Face Discussions with Individuals and Within Teams (بحث‌های رودررو با افراد و درون تیم‌ها) | Contact With Others (ارتباط با دیگران) | Physical Proximity (مجاورت فیزیکی) | Indoors, Environmentally Controlled (محیط داخلی، دارای کنترل محیطی) | Deal With External Customers or the Public in General (سروکار داشتن با مشتریان خارجی یا عموم مردم) | Freedom to Make Decisions (آزادی در تصمیم‌گیری) | Determine Tasks, Priorities and Goals (تعیین وظایف، اولویت‌ها و اهداف) | Work With or Contribute to a Work Group or Team (کار با یا مشارکت در یک گروه کاری یا تیم) | E-Mail (ایمیل) | Telephone Conversations (مکالمات تلفنی) | Spend Time Standing (صرف زمان برای ایستادن) | Time Pressure (فشار زمانی) | Public Speaking (سخنرانی عمومی) | Coordinate or Lead Others in Accomplishing Work Activities (هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری) | Impact of Decisions on Co-workers or Company Results (تأثیر تصمیمات بر همکاران یا نتایج شرکت) | Conflict Situations (موقعیت‌های تعارض) | Dealing With Unpleasant, Angry, or Discourteous People (سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب) | Frequency of Decision Making (تکرار تصمیم‌گیری) | Written Letters and Memos (نامه‌ها و یادداشت‌های کتبی) | Exposed to Disease or Infections (قرار گرفتن در معرض بیماری یا عفونت‌ها)</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | سخنرانی عمومی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Adapted Physical Education Specialists (متخصصان تربیت بدنی تطبیقی) | Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors (مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم) | Career/Technical Education Teachers, Middle School (معلمان آموزش فنی/حرفه‌ای، دوره راهنمایی) | Education Teachers, Postsecondary (معلمان علوم تربیتی، پس از متوسطه) | Education and Childcare Administrators, Preschool and Daycare (مدیران آموزش و مراقبت از کودک، پیش‌دبستانی و مهدکودک) | Educational, Guidance, and Career Counselors and Advisors (مشاوران و راهنمایان آموزشی، تحصیلی و شغلی) | Elementary School Teachers, Except Special Education (معلمان دبستان، به استثنای آموزش ویژه) | Instructional Coordinators (هماهنگ‌کنندگان آموزشی) | Kindergarten Teachers, Except Special Education (معلمان کودکستان، به استثنای آموزش ویژه) | Middle School Teachers, Except Special and Career/Technical Education (معلمان راهنمایی، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Preschool Teachers, Except Special Education (معلمان پیش‌دبستانی، به استثنای آموزش ویژه) | School Psychologists (روان‌شناسان مدرسه) | Secondary School Teachers, Except Special and Career/Technical Education (معلمان متوسطه، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Special Education Teachers, Elementary School (معلمان آموزش ویژه، دبستان) | Special Education Teachers, Middle School (معلمان آموزش ویژه، راهنمایی) | Special Education Teachers, Preschool (معلمان آموزش ویژه، پیش‌دبستانی) | Special Education Teachers, Secondary School (معلمان آموزش ویژه، متوسطه) | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education (دستیاران آموزشی، پیش‌دبستانی، دبستان، راهنمایی و متوسطه، به استثنای آموزش ویژه) | Teaching Assistants, Special Education (دستیاران آموزشی، آموزش ویژه) | Tutors (مدرسان خصوصی)</t>
+          <t>متخصصان تربیت بدنی تطبیقی | مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدرسان علوم تربیتی، آموزش عالی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | روان‌شناسان مدرسه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Special Education Teachers, Elementary School (معلمان آموزش ویژه، دبستان)</t>
+          <t>معلمان آموزش ویژه، دبستان (Special Education Teachers, Elementary School)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>American Sign Language Browser (مرورگر زبان اشاره آمریکایی) | Children's educational software (نرم‌افزار آموزشی کودکان) | Drawing software (نرم‌افزار طراحی) | EasyCBM | Email software (نرم‌افزار ایمیل) | Individualized Educational Program IEP software (نرم‌افزار برنامه آموزش فردی IEP) | Microsoft Excel | Microsoft Office software (نرم‌افزار Microsoft Office) | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Nuance Dragon NaturallySpeaking | Rethink Ed | Scientific Learning Fast ForWord | Screen magnification software (نرم‌افزار بزرگ‌نمایی صفحه) | Screen reader software (نرم‌افزار صفحه‌خوان) | Synapse outSPOKEN | The vOICe Learning Edition | Voice activated software (نرم‌افزار فعال‌شونده با صدا) | Web browser software (نرم‌افزار مرورگر وب) | goQ WordQ</t>
+          <t>American Sign Language Browser (مرورگر زبان اشاره آمریکایی) | Children's educational software | نرم‌افزار طراحی | EasyCBM | نرم‌افزار ایمیل | Individualized Educational Program IEP software (نرم‌افزار برنامه آموزش فردی IEP) | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Nuance Dragon NaturallySpeaking | Rethink Ed | Scientific Learning Fast ForWord | نرم‌افزار بزرگ‌نمایی صفحه | نرم‌افزار صفحه‌خوان | Synapse outSPOKEN | The vOICe Learning Edition | نرم‌افزار فعال‌شونده با صدا | نرم‌افزار مرورگر وب | goQ WordQ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Speaking (سخن‌وری) | Active Listening (گوش دادن فعال) | Reading Comprehension (درک مطلب) | Learning Strategies (راهبردهای یادگیری) | Critical Thinking (تفکر انتقادی) | Writing (نوشتن) | Monitoring (پایش) | Active Learning (یادگیری فعال)</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Education and Training (آموزش و پرورش) | English Language (زبان انگلیسی) | Customer and Personal Service (خدمات مشتری و شخصی) | Computers and Electronics (کامپیوتر و الکترونیک) | Mathematics (ریاضیات) | Administration and Management (اداره و مدیریت) | Psychology (روان‌شناسی) | Public Safety and Security (ایمنی و امنیت عمومی) | Administrative (اداری) | Therapy and Counseling (درمان و مشاوره)</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | مدیریت و اداره | روان‌شناسی | ایمنی و امنیت عمومی | اداری | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Oral Expression (بیان شفاهی) | Oral Comprehension (درک شفاهی) | Problem Sensitivity (حساسیت به مسئله) | Speech Clarity (وضوح گفتار) | Written Comprehension (درک کتبی) | Deductive Reasoning (استدلال قیاسی) | Inductive Reasoning (استدلال استقرایی) | Near Vision (دید نزدیک) | Fluency of Ideas (روانی ایده‌ها) | Speech Recognition (تشخیص گفتار) | Written Expression (بیان کتبی) | Information Ordering (ترتیب‌دهی اطلاعات) | Category Flexibility (انعطاف‌پذیری دسته‌بندی) | Originality (خلاقیت) | Selective Attention (توجه انتخابی) | Flexibility of Closure (انعطاف‌پذیری در بستار) | Far Vision (دید دور)</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | وضوح گفتار | درک کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | روانی ایده‌ها | تشخیص گفتار | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>E-Mail (ایمیل) | Contact With Others (ارتباط با دیگران) | Physical Proximity (مجاورت فیزیکی) | Face-to-Face Discussions with Individuals and Within Teams (بحث‌های رودررو با افراد و درون تیم‌ها) | Work With or Contribute to a Work Group or Team (کار با یا مشارکت در یک گروه کاری یا تیم) | Indoors, Environmentally Controlled (محیط داخلی، دارای کنترل محیطی) | Determine Tasks, Priorities and Goals (تعیین وظایف، اولویت‌ها و اهداف) | Coordinate or Lead Others in Accomplishing Work Activities (هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری) | Telephone Conversations (مکالمات تلفنی) | Spend Time Standing (صرف زمان برای ایستادن) | Freedom to Make Decisions (آزادی در تصمیم‌گیری) | Time Pressure (فشار زمانی)</t>
+          <t>ایمیل | ارتباط با دیگران | نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | صرف زمان برای ایستادن | آزادی در تصمیم‌گیری | فشار زمانی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Adapted Physical Education Specialists (متخصصان تربیت بدنی تطبیقی) | Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors (مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم) | Career/Technical Education Teachers, Middle School (معلمان آموزش فنی/حرفه‌ای، دوره راهنمایی) | Education Administrators, Kindergarten through Secondary (مدیران آموزش، کودکستان تا متوسطه) | Education Teachers, Postsecondary (معلمان علوم تربیتی، پس از متوسطه) | Educational, Guidance, and Career Counselors and Advisors (مشاوران و راهنمایان آموزشی، تحصیلی و شغلی) | Elementary School Teachers, Except Special Education (معلمان دبستان، به استثنای آموزش ویژه) | Instructional Coordinators (هماهنگ‌کنندگان آموزشی) | Kindergarten Teachers, Except Special Education (معلمان کودکستان، به استثنای آموزش ویژه) | Middle School Teachers, Except Special and Career/Technical Education (معلمان راهنمایی، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Preschool Teachers, Except Special Education (معلمان پیش‌دبستانی، به استثنای آموزش ویژه) | School Psychologists (روان‌شناسان مدرسه) | Secondary School Teachers, Except Special and Career/Technical Education (معلمان متوسطه، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Special Education Teachers, Kindergarten (معلمان آموزش ویژه، کودکستان) | Special Education Teachers, Middle School (معلمان آموزش ویژه، راهنمایی) | Special Education Teachers, Preschool (معلمان آموزش ویژه، پیش‌دبستانی) | Special Education Teachers, Secondary School (معلمان آموزش ویژه، متوسطه) | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education (دستیاران آموزشی، پیش‌دبستانی، دبستان، راهنمایی و متوسطه، به استثنای آموزش ویژه) | Teaching Assistants, Special Education (دستیاران آموزشی، آموزش ویژه) | Tutors (مدرسان خصوصی)</t>
+          <t>متخصصان تربیت بدنی تطبیقی | مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدیران آموزشی، مهدکودک تا دبیرستان | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | روان‌شناسان مدرسه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Special Education Teachers, Middle School (معلمان آموزش ویژه، راهنمایی)</t>
+          <t>معلمان آموزش ویژه، راهنمایی (Special Education Teachers, Middle School)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apple macOS | Blackboard software | Common Curriculum | EasyCBM | Email software (نرم‌افزار ایمیل) | Flipgrid | Google Classroom | Hand held spell checkers (غلط‌یاب‌های دستی) | Microsoft Excel | Microsoft Office software (نرم‌افزار Microsoft Office) | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | Padlet | Pear Deck | Schoology | Screen magnification software (نرم‌افزار بزرگ‌نمایی صفحه) | Screen reader software (نرم‌افزار صفحه‌خوان) | Seesaw | Text to speech software (نرم‌افزار تبدیل متن به گفتار) | Video editing software (نرم‌افزار ویرایش ویدیو) | Voice activated software (نرم‌افزار فعال‌شونده با صدا) | Web browser software (نرم‌افزار مرورگر وب)</t>
+          <t>Apple macOS | نرم‌افزار Blackboard | Common Curriculum | EasyCBM | نرم‌افزار ایمیل | Flipgrid | Google Classroom | غلط‌یاب‌های املایی دستی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | Padlet | Pear Deck | Schoology | نرم‌افزار بزرگ‌نمایی صفحه | نرم‌افزار صفحه‌خوان | Seesaw | نرم‌افزار تبدیل متن به گفتار | نرم‌افزار ویرایش ویدیو | نرم‌افزار فعال‌شونده با صدا | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Learning Strategies (راهبردهای یادگیری) | Active Learning (یادگیری فعال) | Speaking (سخن‌وری) | Active Listening (گوش دادن فعال) | Reading Comprehension (درک مطلب) | Writing (نوشتن) | Monitoring (پایش) | Critical Thinking (تفکر انتقادی)</t>
+          <t>راهبردهای یادگیری | یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>English Language (زبان انگلیسی) | Education and Training (آموزش و پرورش) | Mathematics (ریاضیات) | Administrative (اداری) | Customer and Personal Service (خدمات مشتری و شخصی) | Psychology (روان‌شناسی) | Sociology and Anthropology (جامعه‌شناسی و انسان‌شناسی) | Public Safety and Security (ایمنی و امنیت عمومی) | Law and Government (قانون و دولت)</t>
+          <t>زبان انگلیسی | آموزش و پرورش | ریاضیات | اداری | خدمات مشتری و شخصی | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | ایمنی و امنیت عمومی | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Oral Comprehension (درک شفاهی) | Oral Expression (بیان شفاهی) | Written Comprehension (درک کتبی) | Written Expression (بیان کتبی) | Problem Sensitivity (حساسیت به مسئله) | Deductive Reasoning (استدلال قیاسی) | Inductive Reasoning (استدلال استقرایی) | Speech Recognition (تشخیص گفتار) | Speech Clarity (وضوح گفتار) | Information Ordering (ترتیب‌دهی اطلاعات) | Originality (خلاقیت) | Near Vision (دید نزدیک) | Selective Attention (توجه انتخابی) | Category Flexibility (انعطاف‌پذیری دسته‌بندی) | Fluency of Ideas (روانی ایده‌ها)</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | اصالت | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>E-Mail (ایمیل) | Work With or Contribute to a Work Group or Team (کار با یا مشارکت در یک گروه کاری یا تیم) | Face-to-Face Discussions with Individuals and Within Teams (بحث‌های رودررو با افراد و درون تیم‌ها) | Conflict Situations (موقعیت‌های تعارض) | Physical Proximity (مجاورت فیزیکی) | Indoors, Environmentally Controlled (محیط داخلی، دارای کنترل محیطی) | Coordinate or Lead Others in Accomplishing Work Activities (هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری) | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable (قرار گرفتن در معرض صداها و سطوح نویز حواس‌پرت‌کن یا ناراحت‌کننده) | Contact With Others (ارتباط با دیگران) | Dealing With Unpleasant, Angry, or Discourteous People (سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب) | Time Pressure (فشار زمانی) | Determine Tasks, Priorities and Goals (تعیین وظایف، اولویت‌ها و اهداف) | Telephone Conversations (مکالمات تلفنی) | Freedom to Make Decisions (آزادی در تصمیم‌گیری) | Health and Safety of Other Workers (سلامت و ایمنی سایر کارکنان) | Work Outcomes and Results of Other Workers (نتایج کاری و خروجی‌های سایر کارکنان) | Importance of Being Exact or Accurate (اهمیت دقیق یا صحیح بودن) | Spend Time Standing (صرف زمان برای ایستادن) | Frequency of Decision Making (تکرار تصمیم‌گیری)</t>
+          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | موقعیت‌های تعارض | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Adapted Physical Education Specialists (متخصصان تربیت بدنی تطبیقی) | Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors (مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم) | Career/Technical Education Teachers, Middle School (معلمان آموزش فنی/حرفه‌ای، دوره راهنمایی) | Education Teachers, Postsecondary (معلمان علوم تربیتی، پس از متوسطه) | Elementary School Teachers, Except Special Education (معلمان دبستان، به استثنای آموزش ویژه) | Instructional Coordinators (هماهنگ‌کنندگان آموزشی) | Kindergarten Teachers, Except Special Education (معلمان کودکستان، به استثنای آموزش ویژه) | Middle School Teachers, Except Special and Career/Technical Education (معلمان راهنمایی، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Preschool Teachers, Except Special Education (معلمان پیش‌دبستانی، به استثنای آموزش ویژه) | School Psychologists (روان‌شناسان مدرسه) | Secondary School Teachers, Except Special and Career/Technical Education (معلمان متوسطه، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Self-Enrichment Teachers (معلمان دوره‌های فوق‌برنامه) | Special Education Teachers, Elementary School (معلمان آموزش ویژه، دبستان) | Special Education Teachers, Kindergarten (معلمان آموزش ویژه، کودکستان) | Special Education Teachers, Preschool (معلمان آموزش ویژه، پیش‌دبستانی) | Special Education Teachers, Secondary School (معلمان آموزش ویژه، متوسطه) | Teaching Assistants, Postsecondary (دستیاران آموزشی، پس از متوسطه) | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education (دستیاران آموزشی، پیش‌دبستانی، دبستان، راهنمایی و متوسطه، به استثنای آموزش ویژه) | Teaching Assistants, Special Education (دستیاران آموزشی، آموزش ویژه) | Tutors (مدرسان خصوصی)</t>
+          <t>متخصصان تربیت بدنی تطبیقی | مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | روان‌شناسان مدرسه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Special Education Teachers, Secondary School (معلمان آموزش ویژه، متوسطه)</t>
+          <t>معلمان آموزش ویژه، متوسطه (Special Education Teachers, Secondary School)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Email software (نرم‌افزار ایمیل) | Facebook | Hand held spell checkers (غلط‌یاب‌های دستی) | Microsoft Access | Microsoft Excel | Microsoft Office software (نرم‌افزار Microsoft Office) | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | Screen magnification software (نرم‌افزار بزرگ‌نمایی صفحه) | Screen reader software (نرم‌افزار صفحه‌خوان) | Text to speech software (نرم‌افزار تبدیل متن به گفتار) | Video editing software (نرم‌افزار ویرایش ویدیو) | Voice activated software (نرم‌افزار فعال‌شونده با صدا) | Web browser software (نرم‌افزار مرورگر وب)</t>
+          <t>Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | نرم‌افزار ایمیل | Facebook | غلط‌یاب‌های املایی دستی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | نرم‌افزار بزرگ‌نمایی صفحه | نرم‌افزار صفحه‌خوان | نرم‌افزار تبدیل متن به گفتار | نرم‌افزار ویرایش ویدیو | نرم‌افزار فعال‌شونده با صدا | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Learning Strategies (راهبردهای یادگیری) | Reading Comprehension (درک مطلب) | Speaking (سخن‌وری) | Monitoring (پایش) | Active Listening (گوش دادن فعال) | Writing (نوشتن) | Critical Thinking (تفکر انتقادی) | Active Learning (یادگیری فعال)</t>
+          <t>راهبردهای یادگیری | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Education and Training (آموزش و پرورش) | English Language (زبان انگلیسی) | Psychology (روان‌شناسی) | Customer and Personal Service (خدمات مشتری و شخصی) | Therapy and Counseling (درمان و مشاوره) | Administrative (اداری) | Computers and Electronics (کامپیوتر و الکترونیک) | Mathematics (ریاضیات) | Public Safety and Security (ایمنی و امنیت عمومی) | Administration and Management (اداره و مدیریت) | Sociology and Anthropology (جامعه‌شناسی و انسان‌شناسی) | Law and Government (قانون و دولت)</t>
+          <t>آموزش و پرورش | زبان انگلیسی | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | اداری | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oral Expression (بیان شفاهی) | Problem Sensitivity (حساسیت به مسئله) | Speech Clarity (وضوح گفتار) | Oral Comprehension (درک شفاهی) | Written Comprehension (درک کتبی) | Written Expression (بیان کتبی) | Deductive Reasoning (استدلال قیاسی) | Inductive Reasoning (استدلال استقرایی) | Speech Recognition (تشخیص گفتار) | Near Vision (دید نزدیک) | Information Ordering (ترتیب‌دهی اطلاعات) | Fluency of Ideas (روانی ایده‌ها) | Category Flexibility (انعطاف‌پذیری دسته‌بندی) | Selective Attention (توجه انتخابی) | Originality (خلاقیت)</t>
+          <t>بیان شفاهی | حساسیت به مسئله | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Contact With Others (ارتباط با دیگران) | E-Mail (ایمیل) | Face-to-Face Discussions with Individuals and Within Teams (بحث‌های رودررو با افراد و درون تیم‌ها) | Work With or Contribute to a Work Group or Team (کار با یا مشارکت در یک گروه کاری یا تیم) | Coordinate or Lead Others in Accomplishing Work Activities (هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری) | Freedom to Make Decisions (آزادی در تصمیم‌گیری) | Physical Proximity (مجاورت فیزیکی) | Conflict Situations (موقعیت‌های تعارض) | Determine Tasks, Priorities and Goals (تعیین وظایف، اولویت‌ها و اهداف) | Impact of Decisions on Co-workers or Company Results (تأثیر تصمیمات بر همکاران یا نتایج شرکت) | Frequency of Decision Making (تکرار تصمیم‌گیری) | Indoors, Environmentally Controlled (محیط داخلی، دارای کنترل محیطی) | Telephone Conversations (مکالمات تلفنی) | Public Speaking (سخنرانی عمومی) | Time Pressure (فشار زمانی) | Importance of Being Exact or Accurate (اهمیت دقیق یا صحیح بودن) | Dealing With Unpleasant, Angry, or Discourteous People (سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب) | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable (قرار گرفتن در معرض صداها و سطوح نویز حواس‌پرت‌کن یا ناراحت‌کننده)</t>
+          <t>ارتباط با دیگران | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | موقعیت‌های تعارض | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | سخنرانی عمومی | فشار زمانی | اهمیت دقیق یا درست بودن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Adapted Physical Education Specialists (متخصصان تربیت بدنی تطبیقی) | Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors (مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم) | Career/Technical Education Teachers, Middle School (معلمان آموزش فنی/حرفه‌ای، دوره راهنمایی) | Education Administrators, Kindergarten through Secondary (مدیران آموزش، کودکستان تا متوسطه) | Education Teachers, Postsecondary (معلمان علوم تربیتی، پس از متوسطه) | Educational, Guidance, and Career Counselors and Advisors (مشاوران و راهنمایان آموزشی، تحصیلی و شغلی) | Elementary School Teachers, Except Special Education (معلمان دبستان، به استثنای آموزش ویژه) | Instructional Coordinators (هماهنگ‌کنندگان آموزشی) | Kindergarten Teachers, Except Special Education (معلمان کودکستان، به استثنای آموزش ویژه) | Middle School Teachers, Except Special and Career/Technical Education (معلمان راهنمایی، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Preschool Teachers, Except Special Education (معلمان پیش‌دبستانی، به استثنای آموزش ویژه) | Secondary School Teachers, Except Special and Career/Technical Education (معلمان متوسطه، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Self-Enrichment Teachers (معلمان دوره‌های فوق‌برنامه) | Special Education Teachers, Elementary School (معلمان آموزش ویژه، دبستان) | Special Education Teachers, Kindergarten (معلمان آموزش ویژه، کودکستان) | Special Education Teachers, Middle School (معلمان آموزش ویژه، راهنمایی) | Special Education Teachers, Preschool (معلمان آموزش ویژه، پیش‌دبستانی) | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education (دستیاران آموزشی، پیش‌دبستانی، دبستان، راهنمایی و متوسطه، به استثنای آموزش ویژه) | Teaching Assistants, Special Education (دستیاران آموزشی، آموزش ویژه) | Tutors (مدرسان خصوصی)</t>
+          <t>متخصصان تربیت بدنی تطبیقی | مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدیران آموزشی، مهدکودک تا دبیرستان | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Special Education Teachers, All Other (معلمان آموزش ویژه، سایر موارد)</t>
+          <t>معلمان آموزش ویژه، سایر موارد (Special Education Teachers, All Other)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Learning management system LMS (نرم‌افزار سیستم مدیریت یادگیری LMS) | Blackboard software | Microsoft PowerPoint | Microsoft Word | Microsoft Excel | Email software (نرم‌افزار ایمیل) | Google Docs | Web browser software (نرم‌افزار مرورگر وب) | Microsoft Outlook | Database software (نرم‌افزار پایگاه داده) | Graphic presentation software (نرم‌افزار ارائه گرافیکی) | Microsoft Office software (نرم‌افزار Microsoft Office)</t>
+          <t>سیستم مدیریت یادگیری LMS | نرم‌افزار Blackboard | Microsoft PowerPoint | Microsoft Word | Microsoft Excel | نرم‌افزار ایمیل | Google Docs | نرم‌افزار مرورگر وب | Microsoft Outlook | نرم‌افزار پایگاه داده | نرم‌افزار ارائه گرافیکی | نرم‌افزار Microsoft Office</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Speaking (سخن‌وری) | Active Listening (گوش دادن فعال) | Reading Comprehension (درک مطلب) | Critical Thinking (تفکر انتقادی) | Learning Strategies (راهبردهای یادگیری) | Writing (نوشتن) | Active Learning (یادگیری فعال) | Monitoring (پایش)</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Education and Training (آموزش و پرورش) | Psychology (روان‌شناسی) | English Language (زبان انگلیسی) | Therapy and Counseling (درمان و مشاوره) | Customer and Personal Service (خدمات مشتری و شخصی) | Sociology and Anthropology (جامعه‌شناسی و انسان‌شناسی) | Computers and Electronics (کامپیوتر و الکترونیک) | Law and Government (قانون و دولت)</t>
+          <t>آموزش و پرورش | روان‌شناسی | زبان انگلیسی | درمان و مشاوره | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Oral Comprehension (درک شفاهی) | Written Comprehension (درک کتبی) | Oral Expression (بیان شفاهی) | Written Expression (بیان کتبی) | Deductive Reasoning (استدلال قیاسی) | Inductive Reasoning (استدلال استقرایی) | Information Ordering (ترتیب‌دهی اطلاعات) | Problem Sensitivity (حساسیت به مسئله) | Near Vision (دید نزدیک) | Speech Clarity (وضوح گفتار) | Speech Recognition (تشخیص گفتار) | Category Flexibility (انعطاف‌پذیری دسته‌بندی) | Fluency of Ideas (روانی ایده‌ها) | Originality (خلاقیت) | Selective Attention (توجه انتخابی) | Time Sharing (اشتراک زمانی) | Visualization (تجسم) | Memorization (حافظه)</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Face-to-Face Discussions with Individuals and Within Teams (بحث‌های رودررو با افراد و درون تیم‌ها) | Public Speaking (سخنرانی عمومی) | Contact With Others (ارتباط با دیگران) | Indoors, Environmentally Controlled (محیط داخلی، دارای کنترل محیطی) | Deal With External Customers or the Public in General (سروکار داشتن با مشتریان خارجی یا عموم مردم) | Freedom to Make Decisions (آزادی در تصمیم‌گیری) | Determine Tasks, Priorities and Goals (تعیین وظایف، اولویت‌ها و اهداف) | Work With or Contribute to a Work Group or Team (کار با یا مشارکت در یک گروه کاری یا تیم) | E-Mail (ایمیل) | Telephone Conversations (مکالمات تلفنی) | Spend Time Standing (صرف زمان برای ایستادن) | Time Pressure (فشار زمانی) | Written Letters and Memos (نامه‌ها و یادداشت‌های کتبی) | Impact of Decisions on Co-workers or Company Results (تأثیر تصمیمات بر همکاران یا نتایج شرکت) | Coordinate or Lead Others in Accomplishing Work Activities (هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری) | Conflict Situations (موقعیت‌های تعارض) | Frequency of Decision Making (تکرار تصمیم‌گیری) | Physical Proximity (مجاورت فیزیکی) | Dealing With Unpleasant, Angry, or Discourteous People (سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب) | Dealing with Violent or Physically Aggressive People (سروکار داشتن با افراد خشن یا دارای پرخاشگری فیزیکی)</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Special Education Teachers, Preschool (معلمان آموزش ویژه، پیش‌دبستانی) | Special Education Teachers, Kindergarten (معلمان آموزش ویژه، کودکستان) | Special Education Teachers, Elementary School (معلمان آموزش ویژه، دبستان) | Special Education Teachers, Middle School (معلمان آموزش ویژه، راهنمایی) | Special Education Teachers, Secondary School (معلمان آموزش ویژه، متوسطه) | Adapted Physical Education Specialists (متخصصان تربیت بدنی تطبیقی) | Teaching Assistants, Special Education (دستیاران آموزشی، آموزش ویژه) | Elementary School Teachers, Except Special Education (معلمان دبستان، به استثنای آموزش ویژه) | Middle School Teachers, Except Special and Career/Technical Education (معلمان راهنمایی، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Secondary School Teachers, Except Special and Career/Technical Education (معلمان متوسطه، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Kindergarten Teachers, Except Special Education (معلمان کودکستان، به استثنای آموزش ویژه) | Preschool Teachers, Except Special Education (معلمان پیش‌دبستانی، به استثنای آموزش ویژه) | Instructional Coordinators (هماهنگ‌کنندگان آموزشی) | Educational, Guidance, and Career Counselors and Advisors (مشاوران و راهنمایان آموزشی، تحصیلی و شغلی) | School Psychologists (روان‌شناسان مدرسه) | Speech-Language Pathologists (آسیب‌شناسان گفتار-زبان) | Occupational Therapists (کاردرمانگران) | Rehabilitation Counselors (مشاوران توانبخشی) | Education Administrators, Kindergarten through Secondary (مدیران آموزش، کودکستان تا متوسطه) | Tutors (مدرسان خصوصی)</t>
+          <t>معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، متوسطه | متخصصان تربیت بدنی تطبیقی | دستیاران آموزشی، آموزش استثنایی | معلمان دبستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مربیان کودکستان، به استثنای آموزش استثنایی | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | روان‌شناسان مدرسه | آسیب‌شناسان گفتار و زبان | کاردرمانگران | مشاوران توانبخشی | مدیران آموزشی، مهدکودک تا دبیرستان | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Adapted Physical Education Specialists (متخصصان تربیت بدنی تطبیقی)</t>
+          <t>متخصصان تربیت بدنی تطبیقی (Adapted Physical Education Specialists)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Database software (نرم‌افزار پایگاه داده) | Email software (نرم‌افزار ایمیل) | Facebook | Individualized Educational Program IEP software (نرم‌افزار برنامه آموزش فردی IEP) | Microsoft Excel | Microsoft Office software (نرم‌افزار Microsoft Office) | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Student record software (نرم‌افزار سوابق دانش‌آموزان) | Web browser software (نرم‌افزار مرورگر وب)</t>
+          <t>نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Facebook | Individualized Educational Program IEP software (نرم‌افزار برنامه آموزش فردی IEP) | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Student record software | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Active Learning (یادگیری فعال) | Speaking (سخن‌وری) | Active Listening (گوش دادن فعال) | Reading Comprehension (درک مطلب) | Writing (نوشتن) | Critical Thinking (تفکر انتقادی) | Learning Strategies (راهبردهای یادگیری) | Monitoring (پایش)</t>
+          <t>یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Education and Training (آموزش و پرورش) | Psychology (روان‌شناسی) | English Language (زبان انگلیسی) | Therapy and Counseling (درمان و مشاوره) | Customer and Personal Service (خدمات مشتری و شخصی)</t>
+          <t>آموزش و پرورش | روان‌شناسی | زبان انگلیسی | درمان و مشاوره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Oral Expression (بیان شفاهی) | Oral Comprehension (درک شفاهی) | Written Comprehension (درک کتبی) | Written Expression (بیان کتبی) | Problem Sensitivity (حساسیت به مسئله) | Deductive Reasoning (استدلال قیاسی) | Near Vision (دید نزدیک) | Speech Recognition (تشخیص گفتار) | Speech Clarity (وضوح گفتار) | Fluency of Ideas (روانی ایده‌ها) | Inductive Reasoning (استدلال استقرایی) | Originality (خلاقیت) | Information Ordering (ترتیب‌دهی اطلاعات) | Selective Attention (توجه انتخابی) | Flexibility of Closure (انعطاف‌پذیری در بستار) | Far Vision (دید دور) | Trunk Strength (قدرت تنه) | Static Strength (قدرت ایستا) | Multilimb Coordination (هماهنگی چندعضوی) | Manual Dexterity (مهارت دستی) | Arm-Hand Steadiness (ثبات دست و بازو) | Gross Body Coordination (هماهنگی کلی بدن) | Extent Flexibility (انعطاف‌پذیری گسترده) | Stamina (استقامت) | Category Flexibility (انعطاف‌پذیری دسته‌بندی)</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | استدلال استقرایی | اصالت | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری بستار | بینایی دور | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | هماهنگی کلی بدن | انعطاف‌پذیری دامنه حرکت | استقامت | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Face-to-Face Discussions with Individuals and Within Teams (بحث‌های رودررو با افراد و درون تیم‌ها) | E-Mail (ایمیل) | Physical Proximity (مجاورت فیزیکی) | Freedom to Make Decisions (آزادی در تصمیم‌گیری) | Determine Tasks, Priorities and Goals (تعیین وظایف، اولویت‌ها و اهداف) | Work With or Contribute to a Work Group or Team (کار با یا مشارکت در یک گروه کاری یا تیم) | Spend Time Standing (صرف زمان برای ایستادن) | Contact With Others (ارتباط با دیگران) | Spend Time Walking or Running (صرف زمان برای راه رفتن یا دویدن) | Indoors, Environmentally Controlled (محیط داخلی، دارای کنترل محیطی) | Health and Safety of Other Workers (سلامت و ایمنی سایر کارکنان) | Coordinate or Lead Others in Accomplishing Work Activities (هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری) | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable (قرار گرفتن در معرض صداها و سطوح نویز حواس‌پرت‌کن یا ناراحت‌کننده)</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای ایستادن | ارتباط با دیگران | صرف زمان برای راه رفتن یا دویدن | محیط داخلی، دارای کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors (مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم) | Career/Technical Education Teachers, Middle School (معلمان آموزش فنی/حرفه‌ای، دوره راهنمایی) | Career/Technical Education Teachers, Postsecondary (معلمان آموزش فنی/حرفه‌ای، پس از متوسطه) | Career/Technical Education Teachers, Secondary School (معلمان آموزش فنی/حرفه‌ای، دوره متوسطه) | Elementary School Teachers, Except Special Education (معلمان دبستان، به استثنای آموزش ویژه) | Health Specialties Teachers, Postsecondary (معلمان تخصص‌های بهداشتی، پس از متوسطه) | Instructional Coordinators (هماهنگ‌کنندگان آموزشی) | Kindergarten Teachers, Except Special Education (معلمان کودکستان، به استثنای آموزش ویژه) | Recreation and Fitness Studies Teachers, Postsecondary (معلمان مطالعات تفریحی و تناسب اندام، پس از متوسطه) | Recreational Therapists (درمانگران تفریحی) | School Psychologists (روان‌شناسان مدرسه) | Secondary School Teachers, Except Special and Career/Technical Education (معلمان متوسطه، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Self-Enrichment Teachers (معلمان دوره‌های فوق‌برنامه) | Special Education Teachers, Elementary School (معلمان آموزش ویژه، دبستان) | Special Education Teachers, Kindergarten (معلمان آموزش ویژه، کودکستان) | Special Education Teachers, Middle School (معلمان آموزش ویژه، راهنمایی) | Special Education Teachers, Preschool (معلمان آموزش ویژه، پیش‌دبستانی) | Special Education Teachers, Secondary School (معلمان آموزش ویژه، متوسطه) | Teaching Assistants, Special Education (دستیاران آموزشی، آموزش ویژه) | Tutors (مدرسان خصوصی)</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | معلمان دبستان، به استثنای آموزش استثنایی | استادان تخصص‌های بهداشتی، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | درمانگران تفریحی | روان‌شناسان مدرسه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors (مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم)</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم (Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adobe Photoshop | Blackboard software | Computerized testing software (نرم‌افزار آزمون‌گیری کامپیوتری) | Edmodo | Edpuzzle | Educational software (نرم‌افزار آموزشی) | Facebook | Google Classroom | Google Workspace software (نرم‌افزار Google Workspace) | Kahoot! | Learning management system LMS (نرم‌افزار سیستم مدیریت یادگیری LMS) | Microsoft Excel | Microsoft Office software (نرم‌افزار Microsoft Office) | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | Quizlet | SAP software (نرم‌افزار SAP) | Web browser software (نرم‌افزار مرورگر وب) | Zoom</t>
+          <t>Adobe Photoshop | نرم‌افزار Blackboard | Computerized testing software (نرم‌افزار آزمون‌گیری کامپیوتری) | Edmodo | Edpuzzle | نرم‌افزار آموزشی | Facebook | Google Classroom | نرم‌افزار Google Workspace | Kahoot! | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | Quizlet | نرم‌افزار SAP | نرم‌افزار مرورگر وب | Zoom</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Speaking (سخن‌وری) | Learning Strategies (راهبردهای یادگیری) | Reading Comprehension (درک مطلب) | Active Listening (گوش دادن فعال) | Writing (نوشتن) | Monitoring (پایش) | Critical Thinking (تفکر انتقادی) | Active Learning (یادگیری فعال)</t>
+          <t>سخن گفتن | راهبردهای یادگیری | درک مطلب | گوش دادن فعال | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>English Language (زبان انگلیسی) | Education and Training (آموزش و پرورش) | Customer and Personal Service (خدمات مشتری و شخصی) | Administrative (اداری)</t>
+          <t>زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oral Expression (بیان شفاهی) | Written Comprehension (درک کتبی) | Written Expression (بیان کتبی) | Oral Comprehension (درک شفاهی) | Speech Clarity (وضوح گفتار) | Speech Recognition (تشخیص گفتار) | Near Vision (دید نزدیک) | Deductive Reasoning (استدلال قیاسی) | Problem Sensitivity (حساسیت به مسئله) | Inductive Reasoning (استدلال استقرایی) | Fluency of Ideas (روانی ایده‌ها) | Originality (خلاقیت) | Selective Attention (توجه انتخابی) | Flexibility of Closure (انعطاف‌پذیری در بستار) | Information Ordering (ترتیب‌دهی اطلاعات)</t>
+          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>E-Mail (ایمیل) | Face-to-Face Discussions with Individuals and Within Teams (بحث‌های رودررو با افراد و درون تیم‌ها) | Determine Tasks, Priorities and Goals (تعیین وظایف، اولویت‌ها و اهداف) | Coordinate or Lead Others in Accomplishing Work Activities (هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری) | Contact With Others (ارتباط با دیگران) | Freedom to Make Decisions (آزادی در تصمیم‌گیری) | Physical Proximity (مجاورت فیزیکی) | Indoors, Environmentally Controlled (محیط داخلی، دارای کنترل محیطی) | Importance of Being Exact or Accurate (اهمیت دقیق یا صحیح بودن) | Work With or Contribute to a Work Group or Team (کار با یا مشارکت در یک گروه کاری یا تیم) | Frequency of Decision Making (تکرار تصمیم‌گیری) | Impact of Decisions on Co-workers or Company Results (تأثیر تصمیمات بر همکاران یا نتایج شرکت) | Public Speaking (سخنرانی عمومی)</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ارتباط با دیگران | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سخنرانی عمومی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Career/Technical Education Teachers, Middle School (معلمان آموزش فنی/حرفه‌ای، دوره راهنمایی) | Education Teachers, Postsecondary (معلمان علوم تربیتی، پس از متوسطه) | Educational, Guidance, and Career Counselors and Advisors (مشاوران و راهنمایان آموزشی، تحصیلی و شغلی) | Elementary School Teachers, Except Special Education (معلمان دبستان، به استثنای آموزش ویژه) | English Language and Literature Teachers, Postsecondary (معلمان زبان و ادبیات انگلیسی، پس از متوسطه) | Instructional Coordinators (هماهنگ‌کنندگان آموزشی) | Kindergarten Teachers, Except Special Education (معلمان کودکستان، به استثنای آموزش ویژه) | Middle School Teachers, Except Special and Career/Technical Education (معلمان راهنمایی، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Preschool Teachers, Except Special Education (معلمان پیش‌دبستانی، به استثنای آموزش ویژه) | Secondary School Teachers, Except Special and Career/Technical Education (معلمان متوسطه، به استثنای آموزش ویژه و فنی/حرفه‌ای) | Self-Enrichment Teachers (معلمان دوره‌های فوق‌برنامه) | Special Education Teachers, Elementary School (معلمان آموزش ویژه، دبستان) | Special Education Teachers, Kindergarten (معلمان آموزش ویژه، کودکستان) | Special Education Teachers, Middle School (معلمان آموزش ویژه، راهنمایی) | Special Education Teachers, Preschool (معلمان آموزش ویژه، پیش‌دبستانی) | Special Education Teachers, Secondary School (معلمان آموزش ویژه، متوسطه) | Teaching Assistants, Postsecondary (دستیاران آموزشی، پس از متوسطه) | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education (دستیاران آموزشی، پیش‌دبستانی، دبستان، راهنمایی و متوسطه، به استثنای آموزش ویژه) | Teaching Assistants, Special Education (دستیاران آموزشی، آموزش ویژه) | Tutors (مدرسان خصوصی)</t>
+          <t>معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0035_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0035_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | نگارش</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی | تاریخ و باستان‌شناسی</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | دید نزدیک | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | روانی کلام و ایده | ابتکار | انعطاف‌پذیری طبقه‌بندی | دید دور | توجه انتخابی | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بینایی نزدیک | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مربیان سوادآموزی بزرگسالان و آموزش زبان انگلیسی | استادان هنر، نمایش و موسیقی در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای دوره اول متوسطه | هنرآموزان دوره دوم متوسطه | استادان علوم تربیتی و آموزش در آموزش عالی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | استادان زبان و ادبیات انگلیسی در آموزش عالی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی شخصی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و آمادگی | معلمان آموزش استثنایی دوره اول متوسطه | مربیان آموزش استثنایی پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌آموزگاران مدارس، به‌جز آموزش استثنایی | کمک‌آموزگاران مدارس استثنایی | مدرسان و معلمان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | راهبردهای یادگیری | نگارش | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | راهبردهای یادگیری | نگارش | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | مدیریت و امور اداری | ریاضیات | روان‌شناسی</t>
+          <t>آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | مدیریت و اداره | ریاضیات | روان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | استدلال قیاسی | دید نزدیک | مرتب‌سازی اطلاعات | روانی کلام و ایده | انعطاف‌پذیری طبقه‌بندی | دید دور | ابتکار | توجه انتخابی | اشتراک زمانی | انعطاف‌پذیری در ادراک الگوها | سرعت درک الگوها | به‌خاطرسپاری | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بینایی دور | اصالت | توجه انتخابی | تقسیم توجه | انعطاف‌پذیری بستار | سرعت بستار | حفظ کردن | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی انطباقی | استادان مدیریت و بازرگانی در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای دوره اول متوسطه | استادان و مربیان آموزش فنی‌وحرفه‌ای در آموزش عالی | استادان علوم کامپیوتر در آموزش عالی | مشاوران تحصیلی، شغلی و راهنمایان آموزشی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | استادان علوم خانواده و مصرف‌کننده در آموزش عالی | کارشناسان برنامه‌ریزی و تدوین متون درسی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی شخصی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و آمادگی | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌آموزگاران مدارس استثنایی | کارشناسان آموزش و توسعه منابع انسانی | مدرسان و معلمان خصوصی</t>
+          <t>متخصصان تربیت بدنی انطباقی | استادان علوم اداری و مدیریت، آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | استادان علوم رایانه، آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان آموزش استثنایی | کارشناسان آموزش و توسعه منابع انسانی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | راهبردهای یادگیری | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | راهبردهای یادگیری | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | روان‌شناسی | ایمنی و امنیت عمومی | روان‌درمانی و مشاوره‌ | رایانه و الکترونیک | امور اداری و دفتری | خدمات مشتریان و خدمات فردی</t>
+          <t>زبان انگلیسی | آموزش و پرورش | روان‌شناسی | ایمنی و امنیت عمومی | درمان و مشاوره | رایانه و الکترونیک | اداری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | توجه انتخابی | مرتب‌سازی اطلاعات | دید نزدیک | روانی کلام و ایده | اشتراک زمانی | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | توجه انتخابی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | تقسیم توجه | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی انطباقی | مربیان سوادآموزی بزرگسالان و آموزش زبان انگلیسی | هنرآموزان و معلمان فنی‌وحرفه‌ای دوره اول متوسطه | استادان علوم تربیتی و آموزش در آموزش عالی | مشاوران تحصیلی، شغلی و راهنمایان آموزشی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی، به‌جز آموزش استثنایی | روان‌شناسان مدرسه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی شخصی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و آمادگی | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره دوم متوسطه | کمک‌آموزگاران مدارس، به‌جز آموزش استثنایی | کمک‌آموزگاران مدارس استثنایی | مدرسان و معلمان خصوصی</t>
+          <t>متخصصان تربیت بدنی انطباقی | مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | روان‌شناسان مدارس | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | زبان انگلیسی | روان‌درمانی و مشاوره‌ | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | ریاضیات | رایانه و الکترونیک</t>
+          <t>آموزش و پرورش | روان‌شناسی | زبان انگلیسی | درمان و مشاوره | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | روانی کلام و ایده | ابتکار | توجه انتخابی | اشتراک زمانی | تجسم فضایی | به‌خاطرسپاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>گفت‌وگوی حضوری با همکاران و اولیا | ارتباط نزدیک و مستقیم با دانش‌آموزان | محیط سرپوشیده با تهویهٔ مطبوع | تعیین وظایف، اولویت‌ها و اهداف آموزشی | کار گروهی و تیمی | ایستادن طولانی‌مدت در محیط کلاس | آزادی عمل در تصمیم‌گیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | سخنرانی عمومی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی انطباقی | مربیان سوادآموزی بزرگسالان و آموزش زبان انگلیسی | هنرآموزان و معلمان فنی‌وحرفه‌ای دوره اول متوسطه | استادان علوم تربیتی و آموزش در آموزش عالی | مدیران مراکز پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، شغلی و راهنمایان آموزشی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی، به‌جز آموزش استثنایی | روان‌شناسان مدرسه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره اول متوسطه | مربیان آموزش استثنایی پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | کمک‌آموزگاران مدارس، به‌جز آموزش استثنایی | کمک‌آموزگاران مدارس استثنایی | مدرسان و معلمان خصوصی</t>
+          <t>متخصصان تربیت بدنی انطباقی | مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | روان‌شناسان مدارس | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | ریاضیات | مدیریت و امور اداری | روان‌شناسی | ایمنی و امنیت عمومی | امور اداری و دفتری | روان‌درمانی و مشاوره‌</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | مدیریت و اداره | روان‌شناسی | ایمنی و امنیت عمومی | اداری | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | وضوح گفتار | درک کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | روانی کلام و ایده | تشخیص گفتار | بیان کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | ابتکار | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | دید دور</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | وضوح گفتار | درک کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | روانی ایده‌ها | تشخیص گفتار | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی انطباقی | مربیان سوادآموزی بزرگسالان و آموزش زبان انگلیسی | هنرآموزان و معلمان فنی‌وحرفه‌ای دوره اول متوسطه | مدیران مدارس ابتدایی و متوسطه | استادان علوم تربیتی و آموزش در آموزش عالی | مشاوران تحصیلی، شغلی و راهنمایان آموزشی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی، به‌جز آموزش استثنایی | روان‌شناسان مدرسه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره پیش‌دبستانی و آمادگی | معلمان آموزش استثنایی دوره اول متوسطه | مربیان آموزش استثنایی پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | کمک‌آموزگاران مدارس، به‌جز آموزش استثنایی | کمک‌آموزگاران مدارس استثنایی | مدرسان و معلمان خصوصی</t>
+          <t>متخصصان تربیت بدنی انطباقی | مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | روان‌شناسان مدارس | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | یادگیری فعال | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
+          <t>راهبردهای یادگیری | یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | ریاضیات | امور اداری و دفتری | خدمات مشتریان و خدمات فردی | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی | ایمنی و امنیت عمومی | حقوق و مقررات دولتی</t>
+          <t>زبان انگلیسی | آموزش و پرورش | ریاضیات | اداری | خدمات مشتری و شخصی | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | ایمنی و امنیت عمومی | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | ابتکار | دید نزدیک | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | روانی کلام و ایده</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | اصالت | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی انطباقی | مربیان سوادآموزی بزرگسالان و آموزش زبان انگلیسی | هنرآموزان و معلمان فنی‌وحرفه‌ای دوره اول متوسطه | استادان علوم تربیتی و آموزش در آموزش عالی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی، به‌جز آموزش استثنایی | روان‌شناسان مدرسه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی شخصی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و آمادگی | مربیان آموزش استثنایی پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌آموزگاران مدارس، به‌جز آموزش استثنایی | کمک‌آموزگاران مدارس استثنایی | مدرسان و معلمان خصوصی</t>
+          <t>متخصصان تربیت بدنی انطباقی | مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | روان‌شناسان مدارس | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | درک مطلب | سخن گفتن | نظارت | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال</t>
+          <t>راهبردهای یادگیری | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | روان‌شناسی | خدمات مشتریان و خدمات فردی | روان‌درمانی و مشاوره‌ | امور اداری و دفتری | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مدیریت و امور اداری | جامعه‌شناسی و مردم‌شناسی | حقوق و مقررات دولتی</t>
+          <t>آموزش و پرورش | زبان انگلیسی | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | اداری | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | مرتب‌سازی اطلاعات | روانی کلام و ایده | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی | ابتکار</t>
+          <t>بیان شفاهی | حساسیت به مسئله | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی انطباقی | مربیان سوادآموزی بزرگسالان و آموزش زبان انگلیسی | هنرآموزان و معلمان فنی‌وحرفه‌ای دوره اول متوسطه | مدیران مدارس ابتدایی و متوسطه | استادان علوم تربیتی و آموزش در آموزش عالی | مشاوران تحصیلی، شغلی و راهنمایان آموزشی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی، به‌جز آموزش استثنایی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی شخصی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و آمادگی | معلمان آموزش استثنایی دوره اول متوسطه | مربیان آموزش استثنایی پیش‌دبستانی | کمک‌آموزگاران مدارس، به‌جز آموزش استثنایی | کمک‌آموزگاران مدارس استثنایی | مدرسان و معلمان خصوصی</t>
+          <t>متخصصان تربیت بدنی انطباقی | مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | زبان انگلیسی | روان‌درمانی و مشاوره‌ | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | رایانه و الکترونیک | حقوق و مقررات دولتی</t>
+          <t>آموزش و پرورش | روان‌شناسی | زبان انگلیسی | درمان و مشاوره | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | روانی کلام و ایده | ابتکار | توجه انتخابی | اشتراک زمانی | تجسم فضایی | به‌خاطرسپاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>گفت‌وگوی حضوری با همکاران و ذی‌نفعان | سخنرانی در جمع و تدریس | کار گروهی و تیمی | محیط سرپوشیده با تهویهٔ مطبوع | تعیین وظایف، اولویت‌ها و اهداف کاری | آزادی عمل در تصمیم‌گیری | مواجهه با رفتارهای پرخاشگرانه و موقعیت‌های بحرانی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>معلمان آموزش استثنایی دوره پیش‌دبستانی | معلمان آموزش استثنایی دوره پیش‌دبستانی و آمادگی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره دوم متوسطه | متخصصان تربیت بدنی انطباقی | کمک‌آموزگاران مدارس استثنایی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | مربیان پیش‌دبستانی، به‌جز آموزش استثنایی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مشاوران تحصیلی، شغلی و راهنمایان آموزشی | روان‌شناسان مدرسه | گفتاردرمانگران | کاردرمانگران | مشاوران توانبخشی | مدیران مدارس ابتدایی و متوسطه | مدرسان و معلمان خصوصی</t>
+          <t>معلمان آموزش استثنایی دوره پیش‌دبستانی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | متخصصان تربیت بدنی انطباقی | کمک‌معلمان آموزش استثنایی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مشاوران تحصیلی، شغلی و هدایت استعدادها | روان‌شناسان مدارس | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران | کاردرمانگران | مشاوران توانبخشی | مدیران آموزشی مقاطع ابتدایی و متوسطه | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>یادگیری فعال | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | راهبردهای یادگیری | نظارت</t>
+          <t>یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | زبان انگلیسی | روان‌درمانی و مشاوره‌ | خدمات مشتریان و خدمات فردی</t>
+          <t>آموزش و پرورش | روان‌شناسی | زبان انگلیسی | درمان و مشاوره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | تشخیص گفتار | وضوح گفتار | روانی کلام و ایده | استدلال استقرایی | ابتکار | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | دید دور | قدرت تنه | استحکام و قدرت بدنی | هماهنگی چند اندام | چابکی دستی | ثبات دست و بازو | هماهنگی عمومی بدن | دامنه انعطاف‌پذیری حرکتی | بنیه و استقامت جسمانی | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | استدلال استقرایی | اصالت | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری بستار | بینایی دور | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | هماهنگی کلی بدن | انعطاف‌پذیری دامنه حرکت | استقامت | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مربیان سوادآموزی بزرگسالان و آموزش زبان انگلیسی | هنرآموزان و معلمان فنی‌وحرفه‌ای دوره اول متوسطه | استادان و مربیان آموزش فنی‌وحرفه‌ای در آموزش عالی | هنرآموزان دوره دوم متوسطه | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | استادان علوم و تخصص‌های بهداشتی در آموزش عالی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | استادان علوم ورزشی و اوقات فراغت در آموزش عالی | کاردرمانگران تفریحی و حرکتی | روان‌شناسان مدرسه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی شخصی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و آمادگی | معلمان آموزش استثنایی دوره اول متوسطه | مربیان آموزش استثنایی پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | کمک‌آموزگاران مدارس استثنایی | مدرسان و معلمان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | کارشناسان تفریح‌درمانی | روان‌شناسان مدارس | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | درک مطلب | شنیدن فعال | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
+          <t>سخن گفتن | راهبردهای یادگیری | درک مطلب | گوش دادن فعال | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | خدمات مشتریان و خدمات فردی | امور اداری و دفتری</t>
+          <t>زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | روانی کلام و ایده | ابتکار | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>هنرآموزان و معلمان فنی‌وحرفه‌ای دوره اول متوسطه | استادان علوم تربیتی و آموزش در آموزش عالی | مشاوران تحصیلی، شغلی و راهنمایان آموزشی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | استادان زبان و ادبیات انگلیسی در آموزش عالی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی، به‌جز آموزش استثنایی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی شخصی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و آمادگی | معلمان آموزش استثنایی دوره اول متوسطه | مربیان آموزش استثنایی پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌آموزگاران مدارس، به‌جز آموزش استثنایی | کمک‌آموزگاران مدارس استثنایی | مدرسان و معلمان خصوصی</t>
+          <t>معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
